--- a/product_selector_out/STM32F302 - diff.xlsx
+++ b/product_selector_out/STM32F302 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,21 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1106</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="18">
@@ -713,22 +695,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -740,67 +718,59 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -812,18 +782,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -835,88 +805,76 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -939,7 +897,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -962,99 +920,87 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>24 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1066,18 +1012,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1089,88 +1035,76 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1193,7 +1127,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1216,7 +1150,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1239,7 +1173,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1262,99 +1196,87 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -1366,18 +1288,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1389,88 +1311,76 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1493,7 +1403,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1516,789 +1426,51 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32F302ZE</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32F302ZE</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32F302ZE</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32F302CB</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32F302CB</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32F302RB</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32F302RB</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32F302VE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32F302VE</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32F302VB</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32F302VB</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32F302C8</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32F302C8</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32F302C8</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32F302C8</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32F302C8</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32F302CC</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32F302CC</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32F302K8</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32F302K8</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32F302K8</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>24 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32F302K8</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32F302K8</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32F302RC</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32F302RC</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32F302R8</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32F302R8</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32F302R8</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32F302R8</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32F302R8</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E84"/>
+  <autoFilter ref="A18:E54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F302 - diff.xlsx
+++ b/product_selector_out/STM32F302 - diff.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1152</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1116</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="18">
